--- a/backend/data/site-sheets/QMSPro.xlsx
+++ b/backend/data/site-sheets/QMSPro.xlsx
@@ -708,7 +708,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="E2" t="n">
